--- a/02_DIA_inicio_2026_analisis_assets/rbd_9629_escuela-basica-aliven_nt2_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9629_escuela-basica-aliven_nt2_nucleos.xlsx
@@ -679,13 +679,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{49A33856-5ACE-420D-B41A-B4FCD5568FBB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{104ACAF9-7075-4C07-98DF-90881681B728}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A2B416F-D602-4A5C-A4E9-B1580C3404F0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1C1158A8-604B-4553-A2AD-39D2171B3DF3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5C6F3EB-57C9-4DEE-B315-3503603593ED}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F04C305-5434-4E7C-AD77-D3690C495DD3}"/>
 </file>